--- a/experiment/SwinT2_2CH_bestx4/results_HUTCN_SwinT2_2CH_bestx4.xlsx
+++ b/experiment/SwinT2_2CH_bestx4/results_HUTCN_SwinT2_2CH_bestx4.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E301"/>
+  <dimension ref="A1:E411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5344,7 +5344,7 @@
       <c r="D288" t="n">
         <v>0.00239</v>
       </c>
-      <c r="E288" s="3" t="n">
+      <c r="E288" s="2" t="n">
         <v>32.297</v>
       </c>
     </row>
@@ -5566,6 +5566,1876 @@
         <v>0.00231</v>
       </c>
       <c r="E301" t="n">
+        <v>32.292</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" t="n">
+        <v>5.58e-05</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="E302" t="n">
+        <v>32.24</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" t="n">
+        <v>5.49e-05</v>
+      </c>
+      <c r="C303" t="n">
+        <v>0.00227</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0.00227</v>
+      </c>
+      <c r="E303" t="n">
+        <v>32.255</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" t="n">
+        <v>5.39e-05</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="D304" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="E304" t="n">
+        <v>32.247</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" t="n">
+        <v>5.3e-05</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="D305" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="E305" t="n">
+        <v>32.274</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" t="n">
+        <v>5.21e-05</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="E306" t="n">
+        <v>32.283</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" t="n">
+        <v>5.12e-05</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D307" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E307" t="n">
+        <v>32.263</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" t="n">
+        <v>5.03e-05</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="D308" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="E308" t="n">
+        <v>32.264</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" t="n">
+        <v>4.94e-05</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E309" t="n">
+        <v>32.274</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" t="n">
+        <v>4.85e-05</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D310" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E310" t="n">
+        <v>32.272</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" t="n">
+        <v>4.76e-05</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E311" t="n">
+        <v>32.26</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" t="n">
+        <v>4.68e-05</v>
+      </c>
+      <c r="C312" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D312" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E312" t="n">
+        <v>32.275</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" t="n">
+        <v>4.59e-05</v>
+      </c>
+      <c r="C313" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E313" t="n">
+        <v>32.281</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" t="n">
+        <v>4.5e-05</v>
+      </c>
+      <c r="C314" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E314" t="n">
+        <v>32.266</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" t="n">
+        <v>4.42e-05</v>
+      </c>
+      <c r="C315" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D315" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E315" t="n">
+        <v>32.287</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" t="n">
+        <v>4.33e-05</v>
+      </c>
+      <c r="C316" t="n">
+        <v>0.00228</v>
+      </c>
+      <c r="D316" t="n">
+        <v>0.00228</v>
+      </c>
+      <c r="E316" t="n">
+        <v>32.277</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" t="n">
+        <v>4.25e-05</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0.00227</v>
+      </c>
+      <c r="D317" t="n">
+        <v>0.00227</v>
+      </c>
+      <c r="E317" t="n">
+        <v>32.269</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" t="n">
+        <v>4.17e-05</v>
+      </c>
+      <c r="C318" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="D318" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="E318" t="n">
+        <v>32.251</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" t="n">
+        <v>4.08e-05</v>
+      </c>
+      <c r="C319" t="n">
+        <v>0.00228</v>
+      </c>
+      <c r="D319" t="n">
+        <v>0.00228</v>
+      </c>
+      <c r="E319" t="n">
+        <v>32.266</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" t="n">
+        <v>4e-05</v>
+      </c>
+      <c r="C320" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D320" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E320" t="n">
+        <v>32.269</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" t="n">
+        <v>3.92e-05</v>
+      </c>
+      <c r="C321" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D321" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E321" t="n">
+        <v>32.281</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" t="n">
+        <v>3.84e-05</v>
+      </c>
+      <c r="C322" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D322" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E322" t="n">
+        <v>32.264</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" t="n">
+        <v>3.76e-05</v>
+      </c>
+      <c r="C323" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="D323" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="E323" t="n">
+        <v>32.261</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" t="n">
+        <v>3.68e-05</v>
+      </c>
+      <c r="C324" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D324" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E324" t="n">
+        <v>32.282</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" t="n">
+        <v>3.6e-05</v>
+      </c>
+      <c r="C325" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D325" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E325" t="n">
+        <v>32.276</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" t="n">
+        <v>3.53e-05</v>
+      </c>
+      <c r="C326" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D326" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E326" t="n">
+        <v>32.279</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" t="n">
+        <v>3.45e-05</v>
+      </c>
+      <c r="C327" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E327" t="n">
+        <v>32.237</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" t="n">
+        <v>3.38e-05</v>
+      </c>
+      <c r="C328" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="D328" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="E328" t="n">
+        <v>32.27</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" t="n">
+        <v>3.3e-05</v>
+      </c>
+      <c r="C329" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D329" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E329" t="n">
+        <v>32.275</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" t="n">
+        <v>3.23e-05</v>
+      </c>
+      <c r="C330" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D330" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E330" s="3" t="n">
+        <v>32.302</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" t="n">
+        <v>3.15e-05</v>
+      </c>
+      <c r="C331" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D331" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E331" t="n">
+        <v>32.285</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" t="n">
+        <v>3.08e-05</v>
+      </c>
+      <c r="C332" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="D332" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="E332" t="n">
+        <v>32.276</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" t="n">
+        <v>3.01e-05</v>
+      </c>
+      <c r="C333" t="n">
+        <v>0.00226</v>
+      </c>
+      <c r="D333" t="n">
+        <v>0.00226</v>
+      </c>
+      <c r="E333" t="n">
+        <v>32.278</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" t="n">
+        <v>2.94e-05</v>
+      </c>
+      <c r="C334" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E334" t="n">
+        <v>32.278</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" t="n">
+        <v>2.87e-05</v>
+      </c>
+      <c r="C335" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="D335" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="E335" t="n">
+        <v>32.289</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" t="n">
+        <v>2.8e-05</v>
+      </c>
+      <c r="C336" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="D336" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="E336" t="n">
+        <v>32.293</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" t="n">
+        <v>2.73e-05</v>
+      </c>
+      <c r="C337" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D337" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E337" t="n">
+        <v>32.294</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" t="n">
+        <v>2.66e-05</v>
+      </c>
+      <c r="C338" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="E338" t="n">
+        <v>32.28</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" t="n">
+        <v>2.6e-05</v>
+      </c>
+      <c r="C339" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="D339" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="E339" t="n">
+        <v>32.281</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" t="n">
+        <v>2.53e-05</v>
+      </c>
+      <c r="C340" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D340" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E340" t="n">
+        <v>32.264</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" t="n">
+        <v>2.46e-05</v>
+      </c>
+      <c r="C341" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E341" t="n">
+        <v>32.295</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" t="n">
+        <v>2.4e-05</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="E342" t="n">
+        <v>32.272</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" t="n">
+        <v>2.34e-05</v>
+      </c>
+      <c r="C343" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D343" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E343" t="n">
+        <v>32.298</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" t="n">
+        <v>2.27e-05</v>
+      </c>
+      <c r="C344" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D344" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E344" t="n">
+        <v>32.28</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" t="n">
+        <v>2.21e-05</v>
+      </c>
+      <c r="C345" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E345" t="n">
+        <v>32.28</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" t="n">
+        <v>2.15e-05</v>
+      </c>
+      <c r="C346" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="D346" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="E346" t="n">
+        <v>32.288</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" t="n">
+        <v>2.09e-05</v>
+      </c>
+      <c r="C347" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D347" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E347" t="n">
+        <v>32.288</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" t="n">
+        <v>2.03e-05</v>
+      </c>
+      <c r="C348" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="D348" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="E348" t="n">
+        <v>32.292</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" t="n">
+        <v>1.97e-05</v>
+      </c>
+      <c r="C349" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="D349" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="E349" t="n">
+        <v>32.292</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" t="n">
+        <v>1.91e-05</v>
+      </c>
+      <c r="C350" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D350" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E350" t="n">
+        <v>32.288</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" t="n">
+        <v>1.86e-05</v>
+      </c>
+      <c r="C351" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="D351" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="E351" t="n">
+        <v>32.294</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" t="n">
+        <v>1.8e-05</v>
+      </c>
+      <c r="C352" t="n">
+        <v>0.00227</v>
+      </c>
+      <c r="D352" t="n">
+        <v>0.00227</v>
+      </c>
+      <c r="E352" t="n">
+        <v>32.292</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" t="n">
+        <v>1.74e-05</v>
+      </c>
+      <c r="C353" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="D353" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="E353" t="n">
+        <v>32.276</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" t="n">
+        <v>1.69e-05</v>
+      </c>
+      <c r="C354" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D354" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E354" t="n">
+        <v>32.264</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" t="n">
+        <v>1.64e-05</v>
+      </c>
+      <c r="C355" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E355" t="n">
+        <v>32.281</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" t="n">
+        <v>1.58e-05</v>
+      </c>
+      <c r="C356" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D356" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E356" t="n">
+        <v>32.289</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>356</v>
+      </c>
+      <c r="B357" t="n">
+        <v>1.53e-05</v>
+      </c>
+      <c r="C357" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D357" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E357" t="n">
+        <v>32.296</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>357</v>
+      </c>
+      <c r="B358" t="n">
+        <v>1.48e-05</v>
+      </c>
+      <c r="C358" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="D358" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="E358" t="n">
+        <v>32.294</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>358</v>
+      </c>
+      <c r="B359" t="n">
+        <v>1.43e-05</v>
+      </c>
+      <c r="C359" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D359" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E359" t="n">
+        <v>32.295</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" t="n">
+        <v>1.38e-05</v>
+      </c>
+      <c r="C360" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="D360" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="E360" t="n">
+        <v>32.293</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" t="n">
+        <v>1.33e-05</v>
+      </c>
+      <c r="C361" t="n">
+        <v>0.00228</v>
+      </c>
+      <c r="D361" t="n">
+        <v>0.00228</v>
+      </c>
+      <c r="E361" t="n">
+        <v>32.289</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" t="n">
+        <v>1.29e-05</v>
+      </c>
+      <c r="C362" t="n">
+        <v>0.00228</v>
+      </c>
+      <c r="D362" t="n">
+        <v>0.00228</v>
+      </c>
+      <c r="E362" t="n">
+        <v>32.294</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" t="n">
+        <v>1.24e-05</v>
+      </c>
+      <c r="C363" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="D363" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="E363" t="n">
+        <v>32.295</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" t="n">
+        <v>1.19e-05</v>
+      </c>
+      <c r="C364" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D364" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E364" t="n">
+        <v>32.29</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" t="n">
+        <v>1.15e-05</v>
+      </c>
+      <c r="C365" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D365" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E365" t="n">
+        <v>32.291</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="C366" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="D366" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="E366" t="n">
+        <v>32.288</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" t="n">
+        <v>1.06e-05</v>
+      </c>
+      <c r="C367" t="n">
+        <v>0.00228</v>
+      </c>
+      <c r="D367" t="n">
+        <v>0.00228</v>
+      </c>
+      <c r="E367" t="n">
+        <v>32.29</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" t="n">
+        <v>1.02e-05</v>
+      </c>
+      <c r="C368" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="D368" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="E368" t="n">
+        <v>32.292</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" t="n">
+        <v>9.809999999999999e-06</v>
+      </c>
+      <c r="C369" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D369" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E369" t="n">
+        <v>32.291</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" t="n">
+        <v>9.4e-06</v>
+      </c>
+      <c r="C370" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="D370" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="E370" t="n">
+        <v>32.282</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" t="n">
+        <v>9.01e-06</v>
+      </c>
+      <c r="C371" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D371" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E371" t="n">
+        <v>32.287</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" t="n">
+        <v>8.63e-06</v>
+      </c>
+      <c r="C372" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D372" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E372" t="n">
+        <v>32.279</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" t="n">
+        <v>8.260000000000001e-06</v>
+      </c>
+      <c r="C373" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D373" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E373" t="n">
+        <v>32.283</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" t="n">
+        <v>7.890000000000001e-06</v>
+      </c>
+      <c r="C374" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D374" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E374" t="n">
+        <v>32.287</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" t="n">
+        <v>7.54e-06</v>
+      </c>
+      <c r="C375" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D375" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E375" t="n">
+        <v>32.293</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>375</v>
+      </c>
+      <c r="B376" t="n">
+        <v>7.19e-06</v>
+      </c>
+      <c r="C376" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D376" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E376" t="n">
+        <v>32.293</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" t="n">
+        <v>6.85e-06</v>
+      </c>
+      <c r="C377" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D377" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E377" t="n">
+        <v>32.291</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" t="n">
+        <v>6.52e-06</v>
+      </c>
+      <c r="C378" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D378" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E378" t="n">
+        <v>32.285</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" t="n">
+        <v>6.21e-06</v>
+      </c>
+      <c r="C379" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D379" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E379" t="n">
+        <v>32.289</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" t="n">
+        <v>5.9e-06</v>
+      </c>
+      <c r="C380" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D380" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E380" t="n">
+        <v>32.293</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" t="n">
+        <v>5.6e-06</v>
+      </c>
+      <c r="C381" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="D381" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="E381" t="n">
+        <v>32.293</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>381</v>
+      </c>
+      <c r="B382" t="n">
+        <v>5.31e-06</v>
+      </c>
+      <c r="C382" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D382" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E382" t="n">
+        <v>32.295</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>382</v>
+      </c>
+      <c r="B383" t="n">
+        <v>5.03e-06</v>
+      </c>
+      <c r="C383" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="D383" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="E383" t="n">
+        <v>32.291</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>383</v>
+      </c>
+      <c r="B384" t="n">
+        <v>4.75e-06</v>
+      </c>
+      <c r="C384" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D384" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E384" t="n">
+        <v>32.286</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>384</v>
+      </c>
+      <c r="B385" t="n">
+        <v>4.49e-06</v>
+      </c>
+      <c r="C385" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D385" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E385" t="n">
+        <v>32.284</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>385</v>
+      </c>
+      <c r="B386" t="n">
+        <v>4.24e-06</v>
+      </c>
+      <c r="C386" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="D386" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="E386" t="n">
+        <v>32.286</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>386</v>
+      </c>
+      <c r="B387" t="n">
+        <v>3.99e-06</v>
+      </c>
+      <c r="C387" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="D387" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="E387" t="n">
+        <v>32.289</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>387</v>
+      </c>
+      <c r="B388" t="n">
+        <v>3.76e-06</v>
+      </c>
+      <c r="C388" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="D388" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="E388" t="n">
+        <v>32.294</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>388</v>
+      </c>
+      <c r="B389" t="n">
+        <v>3.54e-06</v>
+      </c>
+      <c r="C389" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="D389" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="E389" t="n">
+        <v>32.292</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>389</v>
+      </c>
+      <c r="B390" t="n">
+        <v>3.32e-06</v>
+      </c>
+      <c r="C390" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D390" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E390" t="n">
+        <v>32.295</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>390</v>
+      </c>
+      <c r="B391" t="n">
+        <v>3.11e-06</v>
+      </c>
+      <c r="C391" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D391" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E391" t="n">
+        <v>32.289</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>391</v>
+      </c>
+      <c r="B392" t="n">
+        <v>2.92e-06</v>
+      </c>
+      <c r="C392" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="D392" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="E392" t="n">
+        <v>32.283</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>392</v>
+      </c>
+      <c r="B393" t="n">
+        <v>2.73e-06</v>
+      </c>
+      <c r="C393" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="D393" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="E393" t="n">
+        <v>32.289</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>393</v>
+      </c>
+      <c r="B394" t="n">
+        <v>2.55e-06</v>
+      </c>
+      <c r="C394" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D394" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E394" t="n">
+        <v>32.29</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>394</v>
+      </c>
+      <c r="B395" t="n">
+        <v>2.39e-06</v>
+      </c>
+      <c r="C395" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D395" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E395" t="n">
+        <v>32.291</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>395</v>
+      </c>
+      <c r="B396" t="n">
+        <v>2.23e-06</v>
+      </c>
+      <c r="C396" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="D396" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="E396" t="n">
+        <v>32.289</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>396</v>
+      </c>
+      <c r="B397" t="n">
+        <v>2.08e-06</v>
+      </c>
+      <c r="C397" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D397" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E397" t="n">
+        <v>32.291</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>397</v>
+      </c>
+      <c r="B398" t="n">
+        <v>1.94e-06</v>
+      </c>
+      <c r="C398" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D398" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E398" t="n">
+        <v>32.293</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>398</v>
+      </c>
+      <c r="B399" t="n">
+        <v>1.81e-06</v>
+      </c>
+      <c r="C399" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D399" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E399" t="n">
+        <v>32.292</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>399</v>
+      </c>
+      <c r="B400" t="n">
+        <v>1.69e-06</v>
+      </c>
+      <c r="C400" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="D400" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="E400" t="n">
+        <v>32.293</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>400</v>
+      </c>
+      <c r="B401" t="n">
+        <v>1.58e-06</v>
+      </c>
+      <c r="C401" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="D401" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="E401" t="n">
+        <v>32.292</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>401</v>
+      </c>
+      <c r="B402" t="n">
+        <v>1.48e-06</v>
+      </c>
+      <c r="C402" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="D402" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="E402" t="n">
+        <v>32.292</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>402</v>
+      </c>
+      <c r="B403" t="n">
+        <v>1.39e-06</v>
+      </c>
+      <c r="C403" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="D403" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="E403" t="n">
+        <v>32.295</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>403</v>
+      </c>
+      <c r="B404" t="n">
+        <v>1.31e-06</v>
+      </c>
+      <c r="C404" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="D404" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="E404" t="n">
+        <v>32.292</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" t="n">
+        <v>1.24e-06</v>
+      </c>
+      <c r="C405" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D405" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E405" t="n">
+        <v>32.289</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" t="n">
+        <v>1.17e-06</v>
+      </c>
+      <c r="C406" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D406" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E406" t="n">
+        <v>32.292</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" t="n">
+        <v>1.12e-06</v>
+      </c>
+      <c r="C407" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D407" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E407" t="n">
+        <v>32.291</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" t="n">
+        <v>1.08e-06</v>
+      </c>
+      <c r="C408" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="D408" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="E408" t="n">
+        <v>32.291</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" t="n">
+        <v>1.04e-06</v>
+      </c>
+      <c r="C409" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="D409" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="E409" t="n">
+        <v>32.292</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" t="n">
+        <v>1.02e-06</v>
+      </c>
+      <c r="C410" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="D410" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="E410" t="n">
+        <v>32.293</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="C411" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="D411" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="E411" t="n">
         <v>32.292</v>
       </c>
     </row>
